--- a/DataAnalysis/LC/0.3/Results.xlsx
+++ b/DataAnalysis/LC/0.3/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF333ABF-D50B-4C91-AB68-8E99BF949C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3090B87-9301-41AE-922E-724B564B3639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,143 +422,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>12.75</v>
+      </c>
+      <c r="C2">
+        <v>1.2076147288491199</v>
+      </c>
+      <c r="D2">
+        <v>14.2</v>
+      </c>
+      <c r="E2">
+        <v>2.964606025914553</v>
+      </c>
+      <c r="F2">
+        <v>16.7</v>
+      </c>
+      <c r="G2">
+        <v>2.9173808649388069</v>
+      </c>
+      <c r="H2">
+        <v>14.550000000000002</v>
+      </c>
+      <c r="I2">
+        <v>1.224870867469428</v>
+      </c>
+      <c r="J2">
+        <v>2.7999999999999994</v>
+      </c>
+      <c r="K2">
+        <v>1.0387551904462469</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>13.9</v>
+      </c>
+      <c r="C3">
+        <v>2.7018512172212614</v>
+      </c>
+      <c r="D3">
+        <v>16.2</v>
+      </c>
+      <c r="E3">
+        <v>1.0368220676663862</v>
+      </c>
+      <c r="F3">
+        <v>18.2</v>
+      </c>
+      <c r="G3">
+        <v>1.6431676725154982</v>
+      </c>
+      <c r="H3">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="I3">
+        <v>0.85472542699720599</v>
+      </c>
+      <c r="J3">
+        <v>2.8</v>
+      </c>
+      <c r="K3">
+        <v>1.1571036638473178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="C4">
+        <v>2.6692695630078278</v>
+      </c>
+      <c r="D4">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2">
-        <v>12.75</v>
-      </c>
-      <c r="F2">
-        <v>1.2076147288491199</v>
-      </c>
-      <c r="G2">
-        <v>14.2</v>
-      </c>
-      <c r="H2">
-        <v>2.964606025914553</v>
-      </c>
-      <c r="I2">
-        <v>16.7</v>
-      </c>
-      <c r="J2">
-        <v>2.9173808649388069</v>
-      </c>
-      <c r="K2">
-        <v>14.550000000000002</v>
-      </c>
-      <c r="L2">
-        <v>1.224870867469428</v>
-      </c>
-      <c r="M2">
-        <v>2.7999999999999994</v>
-      </c>
-      <c r="N2">
-        <v>1.0387551904462469</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3">
-        <v>13.9</v>
-      </c>
-      <c r="F3">
-        <v>2.7018512172212614</v>
-      </c>
-      <c r="G3">
+      <c r="E4">
+        <v>1.8371173070873836</v>
+      </c>
+      <c r="F4">
         <v>16.2</v>
       </c>
-      <c r="H3">
-        <v>1.0368220676663862</v>
-      </c>
-      <c r="I3">
-        <v>18.2</v>
-      </c>
-      <c r="J3">
-        <v>1.6431676725154982</v>
-      </c>
-      <c r="K3">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="L3">
-        <v>0.85472542699720599</v>
-      </c>
-      <c r="M3">
-        <v>2.8</v>
-      </c>
-      <c r="N3">
-        <v>1.1571036638473178</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4">
-        <v>13</v>
-      </c>
-      <c r="F4">
-        <v>2.6692695630078278</v>
-      </c>
       <c r="G4">
-        <v>14</v>
+        <v>5.1063685726747137</v>
       </c>
       <c r="H4">
-        <v>1.8371173070873836</v>
+        <v>14.4</v>
       </c>
       <c r="I4">
-        <v>16.2</v>
+        <v>2.6209625034411439</v>
       </c>
       <c r="J4">
-        <v>5.1063685726747137</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="K4">
-        <v>14.4</v>
-      </c>
-      <c r="L4">
-        <v>2.6209625034411439</v>
-      </c>
-      <c r="M4">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="N4">
         <v>1.6641647888488822</v>
       </c>
     </row>
